--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.58921358230039</v>
+        <v>2.370747207123813</v>
       </c>
       <c r="D2" t="n">
-        <v>12.41198284407422</v>
+        <v>2.01694721216206</v>
       </c>
       <c r="E2" t="n">
-        <v>17.97989411948149</v>
+        <v>2.921732794415742</v>
       </c>
       <c r="F2" t="n">
-        <v>17.88301240489525</v>
+        <v>2.905989515795479</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.02412505124847</v>
+        <v>4.716420320827877</v>
       </c>
       <c r="D3" t="n">
-        <v>28.72535162721362</v>
+        <v>4.667869639422213</v>
       </c>
       <c r="E3" t="n">
-        <v>17.97989411948149</v>
+        <v>2.921732794415742</v>
       </c>
       <c r="F3" t="n">
-        <v>17.88301240489525</v>
+        <v>2.905989515795479</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.71741881378542</v>
+        <v>8.891580557240131</v>
       </c>
       <c r="D4" t="n">
-        <v>49.97844286128016</v>
+        <v>8.121496964958027</v>
       </c>
       <c r="E4" t="n">
-        <v>17.97989411948149</v>
+        <v>2.921732794415742</v>
       </c>
       <c r="F4" t="n">
-        <v>17.88301240489525</v>
+        <v>2.905989515795479</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.72606067955386</v>
+        <v>9.380484860427503</v>
       </c>
       <c r="D5" t="n">
-        <v>57.92846793925949</v>
+        <v>9.413376040129668</v>
       </c>
       <c r="E5" t="n">
-        <v>17.97989411948149</v>
+        <v>2.921732794415742</v>
       </c>
       <c r="F5" t="n">
-        <v>17.88301240489525</v>
+        <v>2.905989515795479</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
